--- a/data/trans_camb/P12_3_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,71</t>
+          <t>-0,13; 4,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,17</t>
+          <t>-2,36; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 7,24</t>
+          <t>-0,7; 6,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,9</t>
+          <t>-4,62; 0,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,97</t>
+          <t>-3,22; 2,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,63</t>
+          <t>-2,3; 6,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,86</t>
+          <t>-1,55; 1,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,27</t>
+          <t>-2,07; 1,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 5,29</t>
+          <t>-0,87; 5,05</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 370,94</t>
+          <t>-7,46; 302,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 103,68</t>
+          <t>-76,4; 127,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 470,49</t>
+          <t>-39,8; 454,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 28,56</t>
+          <t>-68,62; 24,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,25; 80,6</t>
+          <t>-51,19; 69,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 159,98</t>
+          <t>-40,79; 158,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 64,0</t>
+          <t>-35,11; 68,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 46,72</t>
+          <t>-46,51; 49,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 169,44</t>
+          <t>-22,94; 157,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,09</t>
+          <t>-0,63; 3,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,52</t>
+          <t>-0,16; 4,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,23</t>
+          <t>1,81; 9,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,55</t>
+          <t>-5,17; 0,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 0,78</t>
+          <t>-5,13; 0,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 4,28</t>
+          <t>-3,66; 4,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,77</t>
+          <t>-1,85; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,04</t>
+          <t>-1,69; 2,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,91</t>
+          <t>0,46; 5,8</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 172,31</t>
+          <t>-15,87; 165,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 195,22</t>
+          <t>-5,39; 202,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,81; 378,63</t>
+          <t>44,64; 386,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 9,37</t>
+          <t>-52,4; 15,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 12,81</t>
+          <t>-52,26; 12,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 63,69</t>
+          <t>-37,87; 67,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 40,49</t>
+          <t>-29,49; 39,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 43,55</t>
+          <t>-27,17; 45,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 123,89</t>
+          <t>7,29; 123,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,06</t>
+          <t>-1,05; 4,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,41</t>
+          <t>-2,4; 2,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,52</t>
+          <t>0,63; 6,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,32</t>
+          <t>1,78; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,13</t>
+          <t>-3,33; 1,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 5,37</t>
+          <t>-0,28; 5,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,46</t>
+          <t>1,17; 5,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,37</t>
+          <t>-2,22; 1,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,73</t>
+          <t>0,88; 4,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 113,7</t>
+          <t>-19,94; 114,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 66,88</t>
+          <t>-42,64; 75,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 183,01</t>
+          <t>7,66; 176,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,28; 154,01</t>
+          <t>20,48; 142,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 41,06</t>
+          <t>-41,6; 36,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 101,57</t>
+          <t>-4,88; 98,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,69; 115,08</t>
+          <t>18,05; 111,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 28,15</t>
+          <t>-33,66; 30,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,48; 100,48</t>
+          <t>13,96; 104,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,46</t>
+          <t>1,48; 7,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,23</t>
+          <t>2,67; 8,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 8,57</t>
+          <t>-1,69; 8,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,09</t>
+          <t>3,66; 11,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 5,95</t>
+          <t>-1,3; 5,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,92</t>
+          <t>-0,24; 5,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,64</t>
+          <t>3,51; 8,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,47</t>
+          <t>1,86; 6,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,62</t>
+          <t>-1,05; 6,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,9; 235,07</t>
+          <t>19,93; 229,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,95; 292,2</t>
+          <t>41,92; 272,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 247,35</t>
+          <t>-27,34; 213,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40,12; 175,78</t>
+          <t>33,14; 171,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 85,18</t>
+          <t>-12,24; 84,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 89,44</t>
+          <t>-2,02; 88,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,19; 158,94</t>
+          <t>47,71; 162,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,85; 116,79</t>
+          <t>22,47; 118,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 96,43</t>
+          <t>-9,82; 108,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 8,12</t>
+          <t>0,16; 8,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,58</t>
+          <t>-0,61; 7,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 8,48</t>
+          <t>0,94; 8,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 12,11</t>
+          <t>2,8; 12,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,47</t>
+          <t>4,36; 13,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 11,56</t>
+          <t>4,24; 11,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,76</t>
+          <t>2,4; 8,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,0</t>
+          <t>2,98; 9,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,96</t>
+          <t>3,67; 8,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 148,83</t>
+          <t>-0,56; 145,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 140,36</t>
+          <t>-6,79; 139,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10,8; 174,72</t>
+          <t>9,14; 154,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,97; 167,78</t>
+          <t>22,46; 165,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>37,02; 192,37</t>
+          <t>34,15; 195,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,93; 161,33</t>
+          <t>36,77; 172,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,61; 127,28</t>
+          <t>26,09; 130,07</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32,58; 131,62</t>
+          <t>30,83; 132,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>39,12; 131,32</t>
+          <t>37,29; 132,74</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 7,82</t>
+          <t>-3,6; 6,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 1,54</t>
+          <t>-7,97; 1,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 7,47</t>
+          <t>-2,19; 7,25</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 10,8</t>
+          <t>-0,31; 10,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 7,03</t>
+          <t>-3,08; 7,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 6,04</t>
+          <t>-10,92; 6,01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 7,24</t>
+          <t>-0,33; 7,21</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 3,03</t>
+          <t>-3,82; 2,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 4,8</t>
+          <t>-6,89; 5,21</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 95,62</t>
+          <t>-27,83; 82,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 19,5</t>
+          <t>-60,66; 15,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 92,64</t>
+          <t>-16,69; 89,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 97,6</t>
+          <t>-2,69; 94,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 64,42</t>
+          <t>-18,82; 67,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-68,29; 47,86</t>
+          <t>-64,04; 46,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 65,05</t>
+          <t>-2,31; 68,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 28,85</t>
+          <t>-26,53; 29,13</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 41,77</t>
+          <t>-49,06; 46,33</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 12,23</t>
+          <t>-0,29; 11,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,9; 12,09</t>
+          <t>0,09; 11,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,13; 16,0</t>
+          <t>5,82; 16,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,49; 20,36</t>
+          <t>8,58; 20,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,88; 21,22</t>
+          <t>8,72; 21,08</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,1; 19,5</t>
+          <t>10,1; 19,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,85; 15,39</t>
+          <t>6,67; 15,22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,97; 15,76</t>
+          <t>6,9; 15,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,78; 16,86</t>
+          <t>9,53; 16,89</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 199,94</t>
+          <t>-5,77; 196,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5,91; 203,79</t>
+          <t>-0,67; 205,67</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47,17; 267,3</t>
+          <t>44,06; 284,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58,85; 258,37</t>
+          <t>60,4; 248,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>59,05; 271,82</t>
+          <t>63,52; 272,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>68,07; 243,78</t>
+          <t>64,19; 233,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>53,74; 182,19</t>
+          <t>52,49; 184,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>56,34; 188,8</t>
+          <t>55,52; 192,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>75,95; 208,96</t>
+          <t>72,75; 215,89</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,26</t>
+          <t>1,86; 4,32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,55</t>
+          <t>1,15; 3,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,39</t>
+          <t>2,45; 6,3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,41</t>
+          <t>3,32; 6,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,58</t>
+          <t>1,8; 4,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,31</t>
+          <t>2,07; 6,22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,97</t>
+          <t>2,96; 4,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,79</t>
+          <t>1,87; 3,79</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,91</t>
+          <t>3,07; 5,88</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>31,11; 95,5</t>
+          <t>32,08; 92,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>18,88; 76,73</t>
+          <t>20,74; 77,12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>47,95; 140,92</t>
+          <t>47,55; 137,08</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36,74; 81,02</t>
+          <t>36,02; 80,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>18,78; 59,04</t>
+          <t>19,76; 61,45</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,59; 81,16</t>
+          <t>24,13; 80,3</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,3; 80,8</t>
+          <t>40,17; 78,25</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>26,8; 59,55</t>
+          <t>26,48; 61,25</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>45,97; 91,81</t>
+          <t>44,83; 91,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_3_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,41</t>
+          <t>0,06; 4,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,43</t>
+          <t>-2,75; 1,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,95</t>
+          <t>-0,17; 8,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,73</t>
+          <t>-4,59; 1,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,71</t>
+          <t>-3,41; 2,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 6,82</t>
+          <t>-2,36; 6,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,89</t>
+          <t>-1,72; 1,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,41</t>
+          <t>-2,2; 1,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,05</t>
+          <t>-0,18; 5,83</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>135,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 302,22</t>
+          <t>-10,01; 308,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 127,35</t>
+          <t>-78,54; 107,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 454,85</t>
+          <t>-12,87; 537,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 24,64</t>
+          <t>-70,84; 29,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,19; 69,52</t>
+          <t>-53,24; 65,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 158,64</t>
+          <t>-41,12; 163,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 68,27</t>
+          <t>-38,45; 60,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 49,35</t>
+          <t>-48,16; 44,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 157,62</t>
+          <t>-6,22; 193,73</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,1</t>
+          <t>4,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,86</t>
+          <t>-0,38; 3,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,38</t>
+          <t>-0,3; 4,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,1</t>
+          <t>2,18; 9,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,89</t>
+          <t>-5,4; 0,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 0,78</t>
+          <t>-5,33; 1,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,53</t>
+          <t>-0,97; 6,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,74</t>
+          <t>-1,78; 1,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,12</t>
+          <t>-1,7; 2,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,8</t>
+          <t>1,71; 6,94</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158,89%</t>
+          <t>170,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>76,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 165,79</t>
+          <t>-11,86; 155,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 202,02</t>
+          <t>-8,88; 175,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,64; 386,29</t>
+          <t>47,54; 340,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 15,41</t>
+          <t>-53,84; 13,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 12,96</t>
+          <t>-53,8; 19,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 67,22</t>
+          <t>-11,27; 92,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 39,46</t>
+          <t>-28,35; 41,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 45,37</t>
+          <t>-26,95; 44,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 123,58</t>
+          <t>26,12; 143,49</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,14</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>3,33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,09</t>
+          <t>-0,83; 4,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,41</t>
+          <t>-2,45; 2,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,24</t>
+          <t>0,21; 5,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,81</t>
+          <t>1,36; 7,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,86</t>
+          <t>-3,4; 1,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,3</t>
+          <t>0,63; 6,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,19</t>
+          <t>1,25; 5,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,43</t>
+          <t>-2,15; 1,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,8</t>
+          <t>1,03; 5,12</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 114,08</t>
+          <t>-15,73; 121,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 75,34</t>
+          <t>-43,68; 62,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 176,29</t>
+          <t>2,41; 165,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20,48; 142,82</t>
+          <t>16,22; 153,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 36,68</t>
+          <t>-42,78; 38,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 98,61</t>
+          <t>7,35; 121,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,05; 111,94</t>
+          <t>17,25; 106,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 30,46</t>
+          <t>-32,51; 32,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,96; 104,37</t>
+          <t>14,9; 105,7</t>
         </is>
       </c>
     </row>
@@ -1282,24 +1282,24 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>5,47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7,83</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>3,55</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,46</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,84</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6,18</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>4,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,7</t>
+          <t>1,18; 7,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 8,94</t>
+          <t>3,06; 9,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,16</t>
+          <t>2,36; 8,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 11,77</t>
+          <t>3,91; 11,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 5,71</t>
+          <t>-1,11; 6,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,87</t>
+          <t>0,5; 6,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,86</t>
+          <t>3,74; 8,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,59</t>
+          <t>1,99; 6,69</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 6,1</t>
+          <t>2,36; 6,65</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>120,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,93; 229,81</t>
+          <t>19,97; 243,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,92; 272,74</t>
+          <t>49,86; 311,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 213,9</t>
+          <t>38,33; 275,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,14; 171,16</t>
+          <t>37,21; 175,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 84,55</t>
+          <t>-11,04; 88,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 88,59</t>
+          <t>3,71; 96,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,71; 162,01</t>
+          <t>45,99; 164,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,47; 118,15</t>
+          <t>24,7; 122,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 108,73</t>
+          <t>29,52; 122,44</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,1</t>
+          <t>8,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>6,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 8,14</t>
+          <t>0,09; 8,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 7,29</t>
+          <t>-0,76; 7,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,04</t>
+          <t>1,37; 8,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,03</t>
+          <t>2,73; 11,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 13,89</t>
+          <t>4,37; 13,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 11,81</t>
+          <t>4,56; 12,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,83</t>
+          <t>2,59; 8,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 9,15</t>
+          <t>3,01; 8,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,91</t>
+          <t>3,91; 9,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 145,84</t>
+          <t>-1,36; 147,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 139,47</t>
+          <t>-9,52; 124,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,14; 154,98</t>
+          <t>12,1; 158,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,46; 165,1</t>
+          <t>21,75; 161,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>34,15; 195,4</t>
+          <t>35,91; 189,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,77; 172,65</t>
+          <t>36,83; 162,09</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,09; 130,07</t>
+          <t>26,41; 129,81</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>30,83; 132,0</t>
+          <t>29,37; 128,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>37,29; 132,74</t>
+          <t>38,31; 131,07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>4,14</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 6,85</t>
+          <t>-4,8; 6,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,17</t>
+          <t>-8,43; 1,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 7,25</t>
+          <t>-1,92; 6,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 10,43</t>
+          <t>-0,38; 10,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 7,83</t>
+          <t>-3,22; 7,33</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 6,01</t>
+          <t>1,15; 10,27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 7,21</t>
+          <t>-0,29; 7,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,93</t>
+          <t>-3,88; 3,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 5,21</t>
+          <t>0,79; 7,2</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-11,34%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 82,75</t>
+          <t>-34,01; 80,53</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-60,66; 15,39</t>
+          <t>-61,0; 21,65</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 89,42</t>
+          <t>-14,12; 86,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 94,73</t>
+          <t>-3,82; 95,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 67,36</t>
+          <t>-19,43; 69,07</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 46,85</t>
+          <t>4,26; 91,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 68,72</t>
+          <t>-2,34; 69,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 29,13</t>
+          <t>-27,61; 27,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,06; 46,33</t>
+          <t>6,02; 69,44</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11,15</t>
+          <t>11,67</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,15</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,53</t>
+          <t>14,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 11,72</t>
+          <t>-0,25; 11,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 11,78</t>
+          <t>1,04; 12,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,82; 16,5</t>
+          <t>6,02; 16,62</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8,58; 20,44</t>
+          <t>8,21; 20,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,72; 21,08</t>
+          <t>8,49; 20,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,1; 19,32</t>
+          <t>11,09; 20,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,67; 15,22</t>
+          <t>6,74; 15,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,9; 15,72</t>
+          <t>6,64; 15,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,53; 16,89</t>
+          <t>10,52; 17,48</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>126,27%</t>
+          <t>132,12%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>138,61%</t>
+          <t>143,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>133,63%</t>
+          <t>138,81%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 196,26</t>
+          <t>-4,88; 195,57</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 205,67</t>
+          <t>4,74; 196,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44,06; 284,72</t>
+          <t>44,83; 269,11</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60,4; 248,8</t>
+          <t>58,28; 237,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>63,52; 272,89</t>
+          <t>60,79; 240,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>64,19; 233,45</t>
+          <t>79,09; 271,86</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,49; 184,11</t>
+          <t>53,81; 182,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>55,52; 192,09</t>
+          <t>52,99; 187,49</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>72,75; 215,89</t>
+          <t>80,69; 214,02</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>5,84</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,32</t>
+          <t>1,77; 4,34</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,59</t>
+          <t>1,15; 3,5</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,3</t>
+          <t>4,12; 6,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,28</t>
+          <t>3,32; 6,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,79</t>
+          <t>1,77; 4,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,22</t>
+          <t>4,76; 7,65</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,94</t>
+          <t>2,96; 4,92</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,79</t>
+          <t>1,85; 3,77</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,88</t>
+          <t>4,91; 6,82</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>108,11%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>32,08; 92,47</t>
+          <t>30,93; 94,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>20,74; 77,12</t>
+          <t>21,24; 80,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>47,55; 137,08</t>
+          <t>73,28; 157,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36,02; 80,83</t>
+          <t>35,59; 83,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>19,76; 61,45</t>
+          <t>18,96; 60,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,13; 80,3</t>
+          <t>51,69; 99,98</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,17; 78,25</t>
+          <t>40,59; 75,44</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>26,48; 61,25</t>
+          <t>24,64; 58,31</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>44,83; 91,64</t>
+          <t>67,6; 107,19</t>
         </is>
       </c>
     </row>
